--- a/Hardware/Teiliste Stand 18.09.2026.xlsx
+++ b/Hardware/Teiliste Stand 18.09.2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dokumente\Schuldateien\SPL\Handy Garage\Hardware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EE6463D-C331-4440-B723-84A4601C16EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6459F39C-E7AE-4FAA-BC0B-E807A389EAF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="75">
   <si>
     <t>Nr.</t>
   </si>
@@ -106,18 +106,6 @@
     <t>Kann weglassen ist aber vorteilhaft</t>
   </si>
   <si>
-    <t>2zxx</t>
-  </si>
-  <si>
-    <t>Temperaturmesser</t>
-  </si>
-  <si>
-    <t>DS18B20</t>
-  </si>
-  <si>
-    <t>1 bis 6</t>
-  </si>
-  <si>
     <t>Bedienung</t>
   </si>
   <si>
@@ -145,9 +133,6 @@
     <t>Stromversorgung</t>
   </si>
   <si>
-    <t>Netzteil</t>
-  </si>
-  <si>
     <t>y4xx</t>
   </si>
   <si>
@@ -197,17 +182,97 @@
   </si>
   <si>
     <t>ESP32-S3 Microcontroller</t>
+  </si>
+  <si>
+    <t>24V</t>
+  </si>
+  <si>
+    <t>R-78K3.3-0.5 (DC/DC-Wandler) </t>
+  </si>
+  <si>
+    <t>DC DC Wandler</t>
+  </si>
+  <si>
+    <t>Stromversorgung für den esp32</t>
+  </si>
+  <si>
+    <t>Zum steuern des Display</t>
+  </si>
+  <si>
+    <t>Zum Darstellen von Informationen</t>
+  </si>
+  <si>
+    <t>Stecker selbsterklärend</t>
+  </si>
+  <si>
+    <t>Stromversorgung das gesamte system</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kann durch was anderes erstezt werden </t>
+  </si>
+  <si>
+    <t>2xxx</t>
+  </si>
+  <si>
+    <t>3zxx</t>
+  </si>
+  <si>
+    <t>Externes Netzteil</t>
+  </si>
+  <si>
+    <t>PD65W USB-C Schnelllademodul </t>
+  </si>
+  <si>
+    <t>y6xx</t>
+  </si>
+  <si>
+    <t>Gehäuse</t>
+  </si>
+  <si>
+    <t>Magneten</t>
+  </si>
+  <si>
+    <t>Schrauben</t>
+  </si>
+  <si>
+    <t>M4*20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zu benutzen um den Deckel an das Gehäuse zu schrauben </t>
+  </si>
+  <si>
+    <t>Zu benutzen um die Verbinugen der Gehäuse festzuschrauchen</t>
+  </si>
+  <si>
+    <t>Um die Handyablage anzubringen</t>
+  </si>
+  <si>
+    <t>Um die Handygaragen zussamenzushalten</t>
+  </si>
+  <si>
+    <t>IRLB8721</t>
+  </si>
+  <si>
+    <t>Mosfet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Um jedes Lademodul einzeln abzudrehen </t>
+  </si>
+  <si>
+    <t>Schalter/Button</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die Idee ist es dem esp ein Signal zu geben das sich dieser abdrehen kann </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="#,##0.00&quot; €&quot;"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -226,6 +291,18 @@
       <sz val="10"/>
       <name val="Arial"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -248,7 +325,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -286,12 +363,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -312,12 +400,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -326,6 +408,25 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -607,12 +708,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:J10"/>
+  <dimension ref="B2:J16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="14.77734375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="34.88671875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.44140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="20.6640625" customWidth="1"/>
     <col min="9" max="9" width="13.6640625" bestFit="1" customWidth="1"/>
@@ -650,7 +751,7 @@
     </row>
     <row r="3" spans="2:10" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="2">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>9</v>
@@ -659,7 +760,7 @@
         <v>10</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="F3" s="2">
         <v>1</v>
@@ -668,11 +769,12 @@
         <v>11</v>
       </c>
       <c r="H3" s="6">
-        <v>7</v>
+        <f>17/3</f>
+        <v>5.666666666666667</v>
       </c>
       <c r="I3" s="6">
         <f>H3*F3</f>
-        <v>7</v>
+        <v>5.666666666666667</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>12</v>
@@ -680,7 +782,7 @@
     </row>
     <row r="4" spans="2:10" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="2">
-        <v>1101</v>
+        <v>2100</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>14</v>
@@ -698,11 +800,11 @@
         <v>11</v>
       </c>
       <c r="H4" s="6">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="I4" s="6">
         <f>H4*F4</f>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>20</v>
@@ -710,137 +812,304 @@
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B5">
-        <v>2101</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" t="s">
+        <v>2200</v>
+      </c>
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="8" t="s">
-        <v>25</v>
+      <c r="F5">
+        <v>1</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>11</v>
       </c>
       <c r="H5" s="4">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="I5" s="4">
-        <v>4.5</v>
+        <f>H5</f>
+        <v>2</v>
+      </c>
+      <c r="J5" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B6">
-        <v>1201</v>
-      </c>
-      <c r="C6" t="s">
+        <v>1300</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F6">
+      <c r="F6" s="1">
         <v>1</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H6">
-        <v>1.5</v>
-      </c>
-      <c r="I6">
-        <f>H6</f>
-        <v>1.5</v>
+      <c r="H6" s="18">
+        <v>6</v>
+      </c>
+      <c r="I6" s="18">
+        <f t="shared" ref="I6" si="0">F6*H6</f>
+        <v>6</v>
+      </c>
+      <c r="J6" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B7">
-        <v>1301</v>
+        <v>2400</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F7" s="1">
+      <c r="D7" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="E7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F7">
         <v>1</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H7" s="9">
-        <v>5</v>
-      </c>
-      <c r="I7" s="9">
-        <f t="shared" ref="I7" si="0">F7*H7</f>
-        <v>5</v>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B8">
-        <v>1401</v>
+        <v>1500</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-      <c r="G8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F8" s="1">
+        <v>3</v>
+      </c>
+      <c r="G8" s="1" t="s">
         <v>11</v>
+      </c>
+      <c r="H8" s="4">
+        <f>8/3</f>
+        <v>2.6666666666666665</v>
+      </c>
+      <c r="I8" s="4">
+        <f>H8*F8</f>
+        <v>8</v>
+      </c>
+      <c r="J8" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B9">
-        <v>1501</v>
+        <v>3500</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F9" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B10">
-        <v>1511</v>
+        <v>2410</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F10" s="1">
+        <v>30</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="F10" s="15">
         <v>1</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="H10" s="4">
+        <v>3</v>
+      </c>
+      <c r="I10" s="4">
+        <f>H10*F10</f>
+        <v>3</v>
+      </c>
+      <c r="J10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B11">
+        <v>2600</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F11" s="13">
+        <v>4</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J11" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B12">
+        <v>2610</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F12" s="13">
+        <v>8</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J12" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B13">
+        <v>3600</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="F13" s="13">
+        <v>10</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B14">
+        <v>3610</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="F14" s="13">
+        <v>8</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J14" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B15">
+        <v>3510</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E15" t="s">
+        <v>70</v>
+      </c>
+      <c r="F15" s="13">
+        <v>4</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J15" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B16">
+        <v>3400</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="F16" s="13">
+        <v>1</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J16" t="s">
+        <v>74</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -855,20 +1124,20 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="11" t="s">
-        <v>41</v>
+      <c r="F2" s="9" t="s">
+        <v>36</v>
       </c>
       <c r="J2" t="s">
         <v>14</v>
@@ -882,16 +1151,16 @@
         <v>1301</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>43</v>
+        <v>37</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>38</v>
       </c>
       <c r="J3" t="s">
         <v>9</v>
@@ -914,13 +1183,13 @@
         <v>13</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="J4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="K4" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.3">
@@ -936,14 +1205,14 @@
       <c r="E5" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="12" t="s">
-        <v>43</v>
+      <c r="F5" s="10" t="s">
+        <v>38</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="K5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.3">
@@ -960,13 +1229,13 @@
         <v>13</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K6" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.3">
@@ -983,63 +1252,50 @@
         <v>13</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="K7" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B8">
-        <v>2101</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>44</v>
-      </c>
+      <c r="C8" s="2"/>
+      <c r="F8" s="2"/>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B9">
         <v>1201</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B16" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="D18" s="13" t="s">
-        <v>46</v>
+      <c r="D18" s="11" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.3">
@@ -1047,10 +1303,10 @@
         <v>1301</v>
       </c>
       <c r="C19" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D19" t="s">
         <v>42</v>
-      </c>
-      <c r="D19" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.3">
@@ -1061,7 +1317,7 @@
         <v>13</v>
       </c>
       <c r="D20" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.3">
@@ -1072,7 +1328,7 @@
         <v>13</v>
       </c>
       <c r="D21" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.3">
@@ -1083,7 +1339,7 @@
         <v>13</v>
       </c>
       <c r="D22" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.3">
@@ -1094,7 +1350,7 @@
         <v>13</v>
       </c>
       <c r="D23" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -1104,11 +1360,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01E78C08-7F26-4B73-949B-08FC548E7326}">
-  <dimension ref="B2:F7"/>
+  <dimension ref="B2:F9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.3">
@@ -1133,43 +1389,60 @@
         <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>56</v>
       </c>
       <c r="F3" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>23</v>
+      </c>
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
-      </c>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B8" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B9" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>

--- a/Hardware/Teiliste Stand 18.09.2026.xlsx
+++ b/Hardware/Teiliste Stand 18.09.2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dokumente\Schuldateien\SPL\Handy Garage\Hardware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6459F39C-E7AE-4FAA-BC0B-E807A389EAF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27AEF481-D8EC-4085-83A6-DF79FA7229DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="81">
   <si>
     <t>Nr.</t>
   </si>
@@ -263,6 +263,24 @@
   </si>
   <si>
     <t xml:space="preserve">Die Idee ist es dem esp ein Signal zu geben das sich dieser abdrehen kann </t>
+  </si>
+  <si>
+    <t>Büchse</t>
+  </si>
+  <si>
+    <t>Die Büchse für das externe Netzteil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platine </t>
+  </si>
+  <si>
+    <t>Steckplatine zum zussamenbauen</t>
+  </si>
+  <si>
+    <t>3*10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3*10 </t>
   </si>
 </sst>
 </file>
@@ -379,7 +397,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -425,6 +443,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -708,7 +729,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:J16"/>
+  <dimension ref="B2:J18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="14.77734375" bestFit="1" customWidth="1"/>
@@ -1034,6 +1055,9 @@
       <c r="D13" s="12" t="s">
         <v>63</v>
       </c>
+      <c r="E13" t="s">
+        <v>80</v>
+      </c>
       <c r="F13" s="13">
         <v>10</v>
       </c>
@@ -1054,6 +1078,9 @@
       <c r="D14" s="12" t="s">
         <v>63</v>
       </c>
+      <c r="E14" t="s">
+        <v>79</v>
+      </c>
       <c r="F14" s="13">
         <v>8</v>
       </c>
@@ -1105,6 +1132,48 @@
       </c>
       <c r="J16" t="s">
         <v>74</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B17">
+        <v>2420</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="E17" t="s">
+        <v>48</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B18">
+        <v>3620</v>
+      </c>
+      <c r="D18" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="F18" s="19">
+        <v>1</v>
+      </c>
+      <c r="G18" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="J18" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
